--- a/data/trans_dic/P38B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P38B-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de colesterol por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de colesterol por prescripción médica (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,64; 91,71</t>
+          <t>85,93; 91,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,22; 89,11</t>
+          <t>81,75; 88,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,89; 89,14</t>
+          <t>81,41; 89,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86,94; 93,98</t>
+          <t>86,56; 93,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,6; 93,54</t>
+          <t>87,33; 93,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,44; 91,94</t>
+          <t>86,84; 92,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,43; 91,87</t>
+          <t>87,36; 91,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,26; 90,07</t>
+          <t>85,59; 90,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,82; 89,41</t>
+          <t>84,84; 89,53</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>87,15; 93,31</t>
+          <t>86,92; 93,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,01; 90,41</t>
+          <t>83,51; 90,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,25; 89,42</t>
+          <t>82,27; 89,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,64; 94,03</t>
+          <t>87,31; 93,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,56; 91,82</t>
+          <t>84,83; 91,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,15; 90,79</t>
+          <t>84,69; 90,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,31; 92,65</t>
+          <t>88,06; 92,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,06; 89,99</t>
+          <t>85,29; 90,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84,52; 89,33</t>
+          <t>84,22; 89,39</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,37; 87,43</t>
+          <t>81,56; 87,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,64; 89,41</t>
+          <t>83,24; 89,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,35; 88,68</t>
+          <t>22,71; 88,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86,84; 94,5</t>
+          <t>87,04; 94,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,1; 93,47</t>
+          <t>82,76; 93,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,31; 95,28</t>
+          <t>87,55; 95,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,09; 88,88</t>
+          <t>84,0; 88,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84,56; 89,66</t>
+          <t>83,98; 89,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,99; 89,9</t>
+          <t>30,21; 89,74</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,49; 86,98</t>
+          <t>82,62; 87,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,07; 86,46</t>
+          <t>82,1; 86,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,15; 85,03</t>
+          <t>78,63; 84,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83,83; 89,02</t>
+          <t>84,1; 89,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,9; 88,01</t>
+          <t>83,22; 88,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,25; 95,41</t>
+          <t>88,36; 95,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,85; 87,19</t>
+          <t>83,78; 87,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,23; 86,41</t>
+          <t>83,35; 86,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84,09; 90,69</t>
+          <t>84,18; 90,41</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,71; 83,88</t>
+          <t>76,62; 83,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,19; 83,66</t>
+          <t>77,12; 83,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75,87; 84,65</t>
+          <t>76,09; 84,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87,72; 92,08</t>
+          <t>87,68; 92,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,22; 89,35</t>
+          <t>84,47; 89,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,99; 91,35</t>
+          <t>61,21; 91,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,96; 87,82</t>
+          <t>84,13; 87,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>82,11; 86,05</t>
+          <t>81,94; 85,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>66,83; 87,47</t>
+          <t>68,46; 87,23</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38,37; 50,53</t>
+          <t>37,8; 50,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48,38; 60,39</t>
+          <t>47,46; 59,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,72; 56,85</t>
+          <t>35,41; 56,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82,46; 86,98</t>
+          <t>82,46; 86,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84,97; 89,03</t>
+          <t>85,04; 88,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78,22; 84,28</t>
+          <t>78,18; 84,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>74,49; 79,12</t>
+          <t>74,72; 79,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78,07; 82,3</t>
+          <t>77,94; 82,13</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68,6; 76,23</t>
+          <t>68,72; 76,36</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>80,76; 83,48</t>
+          <t>80,87; 83,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>80,55; 83,21</t>
+          <t>80,57; 83,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57,66; 81,54</t>
+          <t>55,96; 81,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86,75; 89,0</t>
+          <t>86,71; 89,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,19; 88,4</t>
+          <t>86,23; 88,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,21; 89,38</t>
+          <t>80,71; 89,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,2; 85,86</t>
+          <t>84,2; 85,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>83,86; 85,59</t>
+          <t>83,82; 85,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>69,79; 84,82</t>
+          <t>71,56; 84,69</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de colesterol por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de colesterol por prescripción médica (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>371174; 397486</t>
+          <t>372454; 398109</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>352821; 382354</t>
+          <t>350795; 381395</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>413713; 450321</t>
+          <t>411288; 449809</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>271643; 293649</t>
+          <t>270449; 292604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>304007; 324638</t>
+          <t>303090; 324792</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>386776; 411393</t>
+          <t>388582; 412764</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>652103; 685230</t>
+          <t>651574; 684648</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>661773; 699083</t>
+          <t>664279; 701315</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>808054; 851806</t>
+          <t>808228; 852944</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>363405; 389110</t>
+          <t>362439; 387836</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>310472; 338126</t>
+          <t>312328; 338030</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>371960; 404376</t>
+          <t>372037; 405889</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>294499; 316001</t>
+          <t>293403; 315493</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>314790; 341811</t>
+          <t>315796; 340527</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>321475; 346853</t>
+          <t>323558; 347388</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>665040; 697712</t>
+          <t>663150; 697806</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>634775; 671590</t>
+          <t>636476; 673965</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>705107; 745218</t>
+          <t>702569; 745730</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>507168; 544948</t>
+          <t>508363; 545589</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>434158; 464086</t>
+          <t>432054; 463047</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136011; 592646</t>
+          <t>151769; 592744</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>225903; 245823</t>
+          <t>226425; 245974</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>137317; 154464</t>
+          <t>136758; 153707</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>145724; 159026</t>
+          <t>146136; 159031</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>742880; 785156</t>
+          <t>742122; 785334</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>578641; 613545</t>
+          <t>574702; 612223</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>225453; 750784</t>
+          <t>252305; 749446</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>948332; 1000057</t>
+          <t>949914; 1000404</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>934668; 984593</t>
+          <t>934939; 984778</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>808063; 879196</t>
+          <t>813091; 877521</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>639968; 679551</t>
+          <t>642018; 680656</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>681608; 723582</t>
+          <t>684239; 723923</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>862048; 932016</t>
+          <t>863154; 936510</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1604112; 1668107</t>
+          <t>1602883; 1665933</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1632156; 1694484</t>
+          <t>1634561; 1696093</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1690888; 1823712</t>
+          <t>1692821; 1818131</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>390178; 426651</t>
+          <t>389685; 425897</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475562; 515396</t>
+          <t>475118; 515957</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>359643; 401274</t>
+          <t>360714; 399685</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>661379; 694238</t>
+          <t>661029; 693857</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>619918; 657662</t>
+          <t>621725; 658832</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>513095; 768546</t>
+          <t>514986; 767632</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1060105; 1108806</t>
+          <t>1062166; 1109208</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1110237; 1163519</t>
+          <t>1107946; 1162553</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>879112; 1150502</t>
+          <t>900459; 1147422</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>102031; 134358</t>
+          <t>100517; 134645</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>135453; 169071</t>
+          <t>132875; 166789</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83509; 136738</t>
+          <t>85158; 135170</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>910588; 960560</t>
+          <t>910574; 959480</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>915880; 959634</t>
+          <t>916662; 958661</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>594389; 640466</t>
+          <t>594090; 641803</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1020740; 1084054</t>
+          <t>1023837; 1083566</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1060106; 1117573</t>
+          <t>1058358; 1115193</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>686297; 762609</t>
+          <t>687495; 763940</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2744144; 2836625</t>
+          <t>2747756; 2837588</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2704095; 2793431</t>
+          <t>2704742; 2797025</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1945543; 2751376</t>
+          <t>1888161; 2748686</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3062542; 3142030</t>
+          <t>3061163; 3142264</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3034585; 3112241</t>
+          <t>3035827; 3114027</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2902765; 3194823</t>
+          <t>2884914; 3186704</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5833272; 5948291</t>
+          <t>5833612; 5954487</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5767872; 5886470</t>
+          <t>5764666; 5889719</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4849676; 5894036</t>
+          <t>4972784; 5885249</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P38B-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,23%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,93; 91,85</t>
+          <t>85,74; 91,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81,75; 88,88</t>
+          <t>81,85; 88,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,41; 89,03</t>
+          <t>81,07; 88,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86,56; 93,65</t>
+          <t>87,18; 94,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>87,33; 93,59</t>
+          <t>87,64; 93,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,84; 92,24</t>
+          <t>86,24; 91,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,36; 91,79</t>
+          <t>87,31; 91,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>85,59; 90,36</t>
+          <t>85,49; 90,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,84; 89,53</t>
+          <t>84,73; 89,24</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,79%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,92; 93,01</t>
+          <t>86,91; 93,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,51; 90,38</t>
+          <t>83,02; 90,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,27; 89,76</t>
+          <t>81,99; 89,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,31; 93,88</t>
+          <t>87,22; 94,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,83; 91,47</t>
+          <t>85,0; 91,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,69; 90,93</t>
+          <t>84,09; 90,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,06; 92,67</t>
+          <t>88,36; 92,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,29; 90,31</t>
+          <t>85,38; 90,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84,22; 89,39</t>
+          <t>84,03; 89,1</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,56; 87,53</t>
+          <t>81,38; 87,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,24; 89,21</t>
+          <t>83,72; 89,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,71; 88,7</t>
+          <t>82,98; 89,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,04; 94,56</t>
+          <t>87,18; 94,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,76; 93,01</t>
+          <t>83,12; 93,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,55; 95,28</t>
+          <t>87,66; 95,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84,0; 88,9</t>
+          <t>83,99; 88,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,98; 89,46</t>
+          <t>84,52; 89,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,21; 89,74</t>
+          <t>85,06; 90,63</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,62; 87,01</t>
+          <t>82,39; 86,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,1; 86,48</t>
+          <t>82,21; 86,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,63; 84,86</t>
+          <t>78,92; 84,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,1; 89,16</t>
+          <t>84,12; 89,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,22; 88,05</t>
+          <t>83,22; 88,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,36; 95,87</t>
+          <t>86,92; 90,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,78; 87,08</t>
+          <t>83,66; 87,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,35; 86,49</t>
+          <t>83,41; 86,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84,18; 90,41</t>
+          <t>83,06; 86,69</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,62; 83,73</t>
+          <t>76,8; 83,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,12; 83,75</t>
+          <t>77,44; 83,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76,09; 84,31</t>
+          <t>72,12; 80,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87,68; 92,03</t>
+          <t>87,34; 91,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,47; 89,51</t>
+          <t>84,44; 89,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,21; 91,24</t>
+          <t>86,83; 90,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,13; 87,85</t>
+          <t>84,0; 87,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>81,94; 85,98</t>
+          <t>82,13; 86,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68,46; 87,23</t>
+          <t>81,66; 85,91</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37,8; 50,64</t>
+          <t>38,47; 50,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47,46; 59,57</t>
+          <t>47,31; 59,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,41; 56,2</t>
+          <t>31,95; 51,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82,46; 86,89</t>
+          <t>82,45; 86,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>85,04; 88,94</t>
+          <t>84,96; 89,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78,18; 84,46</t>
+          <t>75,7; 82,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>74,72; 79,08</t>
+          <t>74,15; 78,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>77,94; 82,13</t>
+          <t>77,78; 82,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68,72; 76,36</t>
+          <t>67,74; 74,61</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>80,87; 83,51</t>
+          <t>80,67; 83,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>80,57; 83,32</t>
+          <t>80,53; 83,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55,96; 81,46</t>
+          <t>78,28; 81,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86,71; 89,01</t>
+          <t>86,75; 89,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,23; 88,45</t>
+          <t>86,25; 88,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,71; 89,15</t>
+          <t>85,79; 88,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,2; 85,95</t>
+          <t>84,19; 85,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>83,82; 85,63</t>
+          <t>83,88; 85,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,56; 84,69</t>
+          <t>82,44; 84,51</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>432364</t>
+          <t>469860</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>400966</t>
+          <t>436501</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>833330</t>
+          <t>906361</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>372454; 398109</t>
+          <t>371631; 398418</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>350795; 381395</t>
+          <t>351212; 381248</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>411288; 449809</t>
+          <t>446372; 486781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>270449; 292604</t>
+          <t>272395; 294968</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>303090; 324792</t>
+          <t>304149; 324815</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>388582; 412764</t>
+          <t>421188; 448686</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>651574; 684648</t>
+          <t>651240; 685141</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>664279; 701315</t>
+          <t>663526; 700828</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>808228; 852944</t>
+          <t>880407; 927183</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389535</t>
+          <t>414680</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>336336</t>
+          <t>371454</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>725871</t>
+          <t>786134</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>362439; 387836</t>
+          <t>362392; 388000</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>312328; 338030</t>
+          <t>310516; 337906</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>372037; 405889</t>
+          <t>396172; 431491</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>293403; 315493</t>
+          <t>293104; 316203</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>315796; 340527</t>
+          <t>316432; 341972</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>323558; 347388</t>
+          <t>355308; 384189</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>663150; 697806</t>
+          <t>665393; 698795</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>636476; 673965</t>
+          <t>637141; 672224</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>702569; 745730</t>
+          <t>761129; 807009</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>371558</t>
+          <t>408515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>153954</t>
+          <t>172102</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>525512</t>
+          <t>580617</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>508363; 545589</t>
+          <t>507248; 545814</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>432054; 463047</t>
+          <t>434559; 464453</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>151769; 592744</t>
+          <t>391361; 424230</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>226425; 245974</t>
+          <t>226790; 245244</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>136758; 153707</t>
+          <t>137360; 153915</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>146136; 159031</t>
+          <t>164365; 178237</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>742122; 785334</t>
+          <t>741964; 783996</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>574702; 612223</t>
+          <t>578412; 615416</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>252305; 749446</t>
+          <t>560626; 597353</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>848764</t>
+          <t>925265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>892218</t>
+          <t>764871</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1740982</t>
+          <t>1690137</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>949914; 1000404</t>
+          <t>947248; 998221</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>934939; 984778</t>
+          <t>936244; 983447</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>813091; 877521</t>
+          <t>892471; 954532</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>642018; 680656</t>
+          <t>642148; 681214</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>684239; 723923</t>
+          <t>684269; 724638</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>863154; 936510</t>
+          <t>746779; 781363</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1602883; 1665933</t>
+          <t>1600518; 1665965</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1634561; 1696093</t>
+          <t>1635658; 1700403</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1692821; 1818131</t>
+          <t>1652871; 1725134</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>381549</t>
+          <t>433406</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>698754</t>
+          <t>739665</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1080303</t>
+          <t>1173071</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>389685; 425897</t>
+          <t>390638; 426282</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475118; 515957</t>
+          <t>477111; 515694</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>360714; 399685</t>
+          <t>408911; 454935</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>661029; 693857</t>
+          <t>658450; 692231</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>621725; 658832</t>
+          <t>621554; 657797</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>514986; 767632</t>
+          <t>721386; 754355</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1062166; 1109208</t>
+          <t>1060524; 1110672</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1107946; 1162553</t>
+          <t>1110455; 1164719</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>900459; 1147422</t>
+          <t>1141504; 1200941</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110107</t>
+          <t>97658</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>618142</t>
+          <t>669951</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>728249</t>
+          <t>767609</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>100517; 134645</t>
+          <t>102308; 133657</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>132875; 166789</t>
+          <t>132461; 166626</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85158; 135170</t>
+          <t>75791; 122394</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>910574; 959480</t>
+          <t>910514; 958492</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>916662; 958661</t>
+          <t>915750; 959666</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>594090; 641803</t>
+          <t>637917; 693984</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1023837; 1083566</t>
+          <t>1016058; 1081818</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1058358; 1115193</t>
+          <t>1056109; 1118644</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>687495; 763940</t>
+          <t>731503; 805786</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2533878</t>
+          <t>2749384</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3100369</t>
+          <t>3154545</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5634247</t>
+          <t>5903929</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2747756; 2837588</t>
+          <t>2741042; 2838162</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2704742; 2797025</t>
+          <t>2703537; 2793337</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1888161; 2748686</t>
+          <t>2693185; 2806183</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3061163; 3142264</t>
+          <t>3062563; 3142386</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3035827; 3114027</t>
+          <t>3036726; 3115347</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2884914; 3186704</t>
+          <t>3115321; 3197601</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5833612; 5954487</t>
+          <t>5833141; 5954449</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5764666; 5889719</t>
+          <t>5769068; 5888776</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4972784; 5885249</t>
+          <t>5830077; 5976524</t>
         </is>
       </c>
     </row>
